--- a/static/data/exports/Retro_UK_AE_2012.xlsx
+++ b/static/data/exports/Retro_UK_AE_2012.xlsx
@@ -3015,7 +3015,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -15231,20 +15231,20 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>1488165</v>
+        <v>1488166</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Jagveer Singh</t>
+          <t>Sardar Khan (Pappu)</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>JLKP</t>
+          <t>RLD</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>16110</v>
+        <v>16073</v>
       </c>
       <c r="E198" t="n">
         <v>141</v>
@@ -15268,12 +15268,12 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Jagveer Singh</t>
+          <t>Sardar Khan (Pappu)</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>JLKP</t>
+          <t>RLD</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -15287,7 +15287,7 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="Q198" t="b">
         <v>0</v>
@@ -15306,20 +15306,20 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1488166</v>
+        <v>1488165</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Sardar Khan (Pappu)</t>
+          <t>Jagveer Singh</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>RLD</t>
+          <t>JLKP</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>16073</v>
+        <v>16110</v>
       </c>
       <c r="E199" t="n">
         <v>141</v>
@@ -15343,12 +15343,12 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Sardar Khan (Pappu)</t>
+          <t>Jagveer Singh</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>RLD</t>
+          <t>JLKP</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -15362,7 +15362,7 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="Q199" t="b">
         <v>0</v>
@@ -23631,11 +23631,11 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>1488860</v>
+        <v>1488859</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Noshad</t>
+          <t>Muhammad Mursalin Qureshi</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>Noshad</t>
+          <t>Muhammad Mursalin Qureshi</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -23687,7 +23687,7 @@
         </is>
       </c>
       <c r="P310" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q310" t="b">
         <v>0</v>
@@ -23706,11 +23706,11 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>1488859</v>
+        <v>1488860</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Muhammad Mursalin Qureshi</t>
+          <t>Noshad</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -23743,7 +23743,7 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Muhammad Mursalin Qureshi</t>
+          <t>Noshad</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -23762,7 +23762,7 @@
         </is>
       </c>
       <c r="P311" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q311" t="b">
         <v>0</v>
@@ -24615,7 +24615,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D323" t="n">
@@ -58290,7 +58290,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D772" t="n">
